--- a/Copy of inflation_data_2007 to 2022 base_yr_july_2001.xlsx
+++ b/Copy of inflation_data_2007 to 2022 base_yr_july_2001.xlsx
@@ -18,10 +18,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="18">
   <si>
-    <t>Year</t>
+    <t>year</t>
   </si>
   <si>
-    <t>Month</t>
+    <t>month</t>
   </si>
   <si>
     <t>moving_avg_inflation</t>
@@ -176,7 +176,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
